--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/antofagasta.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/antofagasta.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>74291.3</v>
+        <v>74805.96000000001</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>29060.14</v>
+        <v>29008.6</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24940.85</v>
+        <v>24896.61</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>17538.84</v>
+        <v>17662.63</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>76733.27</v>
+        <v>76458.12</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>38249.53</v>
+        <v>38166.75</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>38194.57</v>
+        <v>38194.82</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>57937.89</v>
+        <v>59659.98</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>32917.22</v>
+        <v>33459.75</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>23789.71</v>
+        <v>23848.25</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>45793.07</v>
+        <v>45666.75</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>41135.32</v>
+        <v>40551.51</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>29744.15</v>
+        <v>29347.95</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>754.45</v>
+        <v>744.4</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>28862.8</v>
+        <v>29055.99</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>32541.86</v>
+        <v>32361.45</v>
       </c>
     </row>
     <row r="18">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>650188.38</v>
+        <v>654540.41</v>
       </c>
     </row>
     <row r="19">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>36686.67</v>
+        <v>36932.23</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1473.5</v>
+        <v>1483.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/antofagasta.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/antofagasta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4468-245-CM25</t>
+          <t>1999-3-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>60.103.001-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>74805.96000000001</v>
+        <v>21079.54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1080164-33-CM25</t>
+          <t>3506-145-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>29008.6</v>
+        <v>35997.07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1080164-35-CM25</t>
+          <t>2385-121-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24896.61</v>
+        <v>28715.77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>796305-80-CM25</t>
+          <t>2386-10-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.606.207-7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>17662.63</v>
+        <v>15316.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4051-381-CM25</t>
+          <t>1375735-13-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,32 +798,28 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>76458.12</v>
+        <v>25256.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1233822-93-CM25</t>
+          <t>1346284-55-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -833,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.076.481-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -863,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -878,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>38166.75</v>
+        <v>29524.53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2385-11-CM26</t>
+          <t>2429-1752-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -924,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -939,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>38194.82</v>
+        <v>42256.94</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4468-5-CM26</t>
+          <t>2429-1854-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -970,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>59659.98</v>
+        <v>25864.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4468-19-CM26</t>
+          <t>2385-291-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1061,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>33459.75</v>
+        <v>17280.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>650-17-CM26</t>
+          <t>650-37-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>23848.25</v>
+        <v>28761.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4051-43-CM26</t>
+          <t>803-35-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,43 +1179,43 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>45666.75</v>
+        <v>18851.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4051-114-CM26</t>
+          <t>650-56-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,43 +1240,43 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>40551.51</v>
+        <v>28724.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2429-733-CM26</t>
+          <t>4999-127-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,43 +1286,47 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>29347.95</v>
+        <v>72908.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2429-734-CM26</t>
+          <t>1994-65-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>60.511.021-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,43 +1366,43 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>744.4</v>
+        <v>19823.54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>650-72-CM26</t>
+          <t>2385-720-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,28 +1427,28 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>29055.99</v>
+        <v>28170.78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>957865-235-CM26</t>
+          <t>4468-245-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.980.820-7</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,43 +1488,43 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>32361.45</v>
+        <v>74805.96000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1782-12-CM26</t>
+          <t>1080164-35-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,62 +1534,58 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>654540.41</v>
+        <v>24896.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2429-914-CM26</t>
+          <t>1080164-33-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1599,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1614,28 +1610,28 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>36932.23</v>
+        <v>29008.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2429-915-CM26</t>
+          <t>796305-80-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1645,12 +1641,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1660,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1675,7 +1671,991 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
+        <v>17662.63</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4051-381-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.252.600-7</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>76458.12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1233822-93-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>65.076.481-1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>38166.75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2385-11-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>38194.82</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4468-5-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.253.200-7</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>59659.98</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4468-19-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.253.200-7</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>33459.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>650-17-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.814.000-8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>23848.25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4051-43-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.252.600-7</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>45666.75</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4051-114-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.252.600-7</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>40551.51</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2429-733-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>29347.95</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2429-734-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>744.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>650-72-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.814.000-8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>29055.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>957865-235-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.980.820-7</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>32361.45</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1782-12-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>72.224.100-2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Antofagasta</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>654540.41</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2429-914-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>36932.23</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2429-915-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
         <v>1483.36</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3506-597-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.349.970-7</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>29985.76</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/antofagasta.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>957865-235-CM26</t>
+          <t>2429-914-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.980.820-7</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>32361.45</v>
+        <v>36932.23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1782-12-CM26</t>
+          <t>2429-915-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2453,32 +2453,28 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>654540.41</v>
+        <v>1483.36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2429-914-CM26</t>
+          <t>1782-12-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2503,12 +2499,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2518,28 +2514,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>36932.23</v>
+        <v>654540.41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2429-915-CM26</t>
+          <t>3506-597-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2594,67 +2594,6 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1483.36</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>3506-597-CM26</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>69.020.100-3</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>76.349.970-7</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="n">
         <v>29985.76</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/antofagasta.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/antofagasta.xlsx
@@ -562,7 +562,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1403,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1468,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1533,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1598,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1663,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1728,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1790,7 +1858,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1851,7 +1923,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1912,7 +1988,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1973,7 +2053,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2034,7 +2118,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2095,7 +2183,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2156,7 +2248,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2217,7 +2313,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2278,7 +2378,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2339,7 +2443,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2400,7 +2508,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2461,7 +2573,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/antofagasta.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2460,7 +2460,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2429-914-CM26</t>
+          <t>2429-915-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>36932.23</v>
+        <v>1483.36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2429-915-CM26</t>
+          <t>1782-12-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1483.36</v>
+        <v>654540.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1782-12-CM26</t>
+          <t>2429-914-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>654540.41</v>
+        <v>36932.23</v>
       </c>
     </row>
     <row r="35">
@@ -2711,6 +2711,132 @@
       </c>
       <c r="M35" s="2" t="n">
         <v>29985.76</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2385-774-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SKC Transportes S.A.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.176.602-3</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>23003.62</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3834-364-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>AUTOMOTORA DEL PACIFICO SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>76.717.353-9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>17202.18</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/antofagasta.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/antofagasta.xlsx
@@ -2220,7 +2220,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
